--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>126693623</v>
       </c>
       <c r="B6" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>126693619</v>
       </c>
       <c r="B7" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>126693620</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>126693608</v>
       </c>
       <c r="B9" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126693629</v>
+        <v>126693628</v>
       </c>
       <c r="B10" t="n">
-        <v>91245</v>
+        <v>110527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696922</v>
+        <v>697012</v>
       </c>
       <c r="R10" t="n">
-        <v>6607606</v>
+        <v>6607512</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,32 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126693628</v>
+        <v>126693629</v>
       </c>
       <c r="B11" t="n">
-        <v>110452</v>
+        <v>91319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697012</v>
+        <v>696922</v>
       </c>
       <c r="R11" t="n">
-        <v>6607512</v>
+        <v>6607606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>126693623</v>
       </c>
       <c r="B6" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>126693619</v>
       </c>
       <c r="B7" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>126693620</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>126693608</v>
       </c>
       <c r="B9" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126693628</v>
+        <v>126693629</v>
       </c>
       <c r="B10" t="n">
-        <v>110527</v>
+        <v>91325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697012</v>
+        <v>696922</v>
       </c>
       <c r="R10" t="n">
-        <v>6607512</v>
+        <v>6607606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,32 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126693629</v>
+        <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>91319</v>
+        <v>110533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696922</v>
+        <v>697012</v>
       </c>
       <c r="R11" t="n">
-        <v>6607606</v>
+        <v>6607512</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1532,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126693629</v>
+        <v>126693628</v>
       </c>
       <c r="B10" t="n">
-        <v>91325</v>
+        <v>110533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696922</v>
+        <v>697012</v>
       </c>
       <c r="R10" t="n">
-        <v>6607606</v>
+        <v>6607512</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,32 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126693628</v>
+        <v>126693629</v>
       </c>
       <c r="B11" t="n">
-        <v>110533</v>
+        <v>91325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697012</v>
+        <v>696922</v>
       </c>
       <c r="R11" t="n">
-        <v>6607512</v>
+        <v>6607606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>126693623</v>
       </c>
       <c r="B6" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>126693619</v>
       </c>
       <c r="B7" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>126693608</v>
       </c>
       <c r="B9" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>126693628</v>
       </c>
       <c r="B10" t="n">
-        <v>110533</v>
+        <v>110534</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>126693629</v>
       </c>
       <c r="B11" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1532,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126693628</v>
+        <v>126693629</v>
       </c>
       <c r="B10" t="n">
-        <v>110534</v>
+        <v>91326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697012</v>
+        <v>696922</v>
       </c>
       <c r="R10" t="n">
-        <v>6607512</v>
+        <v>6607606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,32 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126693629</v>
+        <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>91326</v>
+        <v>110534</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696922</v>
+        <v>697012</v>
       </c>
       <c r="R11" t="n">
-        <v>6607606</v>
+        <v>6607512</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>98477</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>126693623</v>
       </c>
       <c r="B6" t="n">
-        <v>91326</v>
+        <v>91319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>126693619</v>
       </c>
       <c r="B7" t="n">
-        <v>100625</v>
+        <v>100618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>126693620</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>126693608</v>
       </c>
       <c r="B9" t="n">
-        <v>100625</v>
+        <v>100618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126693629</v>
+        <v>126693628</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>110527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696922</v>
+        <v>697012</v>
       </c>
       <c r="R10" t="n">
-        <v>6607606</v>
+        <v>6607512</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,32 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126693628</v>
+        <v>126693629</v>
       </c>
       <c r="B11" t="n">
-        <v>110534</v>
+        <v>91319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697012</v>
+        <v>696922</v>
       </c>
       <c r="R11" t="n">
-        <v>6607512</v>
+        <v>6607606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>126693623</v>
       </c>
       <c r="B6" t="n">
-        <v>91319</v>
+        <v>91326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>126693619</v>
       </c>
       <c r="B7" t="n">
-        <v>100618</v>
+        <v>100625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>126693620</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>126693608</v>
       </c>
       <c r="B9" t="n">
-        <v>100618</v>
+        <v>100625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126693628</v>
+        <v>126693629</v>
       </c>
       <c r="B10" t="n">
-        <v>110527</v>
+        <v>91326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697012</v>
+        <v>696922</v>
       </c>
       <c r="R10" t="n">
-        <v>6607512</v>
+        <v>6607606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,32 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126693629</v>
+        <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>91319</v>
+        <v>110534</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696922</v>
+        <v>697012</v>
       </c>
       <c r="R11" t="n">
-        <v>6607606</v>
+        <v>6607512</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>98477</v>
+        <v>99055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,11 @@
           <t>Aivars Dunskis</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1535,7 +1539,7 @@
         <v>126693629</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>91814</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,14 +1629,18 @@
           <t>Aivars Dunskis</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>110534</v>
+        <v>111258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,7 +1730,11 @@
           <t>Aivars Dunskis</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>99055</v>
+        <v>99057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>126693629</v>
       </c>
       <c r="B10" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>111258</v>
+        <v>111272</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>99057</v>
+        <v>99058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>126693629</v>
       </c>
       <c r="B10" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>111272</v>
+        <v>111273</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>99058</v>
+        <v>99059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>126693629</v>
       </c>
       <c r="B10" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>111273</v>
+        <v>111274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>99059</v>
+        <v>99062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>126693629</v>
       </c>
       <c r="B10" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>111274</v>
+        <v>111291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>99062</v>
+        <v>99063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>126693629</v>
       </c>
       <c r="B10" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>111291</v>
+        <v>111296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>99063</v>
+        <v>99069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>126693629</v>
       </c>
       <c r="B10" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>111296</v>
+        <v>111302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>99069</v>
+        <v>99070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>111302</v>
+        <v>111303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>99070</v>
+        <v>99071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>126693629</v>
       </c>
       <c r="B10" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>111303</v>
+        <v>111304</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>126693627</v>
       </c>
       <c r="B5" t="n">
-        <v>99071</v>
+        <v>99074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>126693629</v>
       </c>
       <c r="B10" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>126693628</v>
       </c>
       <c r="B11" t="n">
-        <v>111304</v>
+        <v>111302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89925501</v>
+        <v>126693623</v>
       </c>
       <c r="B2" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barrskog Öst Kvistaren, Upl</t>
+          <t>Boda, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696915.1815178567</v>
+        <v>697013</v>
       </c>
       <c r="R2" t="n">
-        <v>6607617.838599375</v>
+        <v>6607393</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,84 +754,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fingal Gyllang</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fingal Gyllang</t>
+          <t>Amelie Lindhagen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89925465</v>
+        <v>126693629</v>
       </c>
       <c r="B3" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrskog Öst Kvistaren, Upl</t>
+          <t>Boda, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696915.1815178567</v>
+        <v>696922</v>
       </c>
       <c r="R3" t="n">
-        <v>6607617.838599375</v>
+        <v>6607606</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,66 +851,68 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fingal Gyllang</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fingal Gyllang</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89925511</v>
+        <v>89925465</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -975,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696915.1815178567</v>
+        <v>696915</v>
       </c>
       <c r="R4" t="n">
-        <v>6607617.838599375</v>
+        <v>6607618</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1008,27 +953,18 @@
           <t>2021-01-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-01-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1047,48 +983,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126693627</v>
+        <v>114931948</v>
       </c>
       <c r="B5" t="n">
-        <v>99079</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Boda, Upl</t>
+          <t>Storkärret, Storkärret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697005</v>
+        <v>697064</v>
       </c>
       <c r="R5" t="n">
-        <v>6607495</v>
+        <v>6607550</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,12 +1049,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,48 +1079,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Stora Obrutna Skogsområden</t>
+          <t>Nya Tärnan gruppen</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126693623</v>
+        <v>126693620</v>
       </c>
       <c r="B6" t="n">
-        <v>91326</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697013</v>
+        <v>696957</v>
       </c>
       <c r="R6" t="n">
-        <v>6607393</v>
+        <v>6607497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126693619</v>
+        <v>89925535</v>
       </c>
       <c r="B7" t="n">
-        <v>100625</v>
+        <v>56925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,37 +1203,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100045</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Boda, Upl</t>
+          <t>Barrskog Öst Kvistaren, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696859</v>
+        <v>696915</v>
       </c>
       <c r="R7" t="n">
-        <v>6607593</v>
+        <v>6607618</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,12 +1269,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2021-01-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hörda.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,60 +1294,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Fingal Gyllang</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
+          <t>Fingal Gyllang</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126693620</v>
+        <v>114930157</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Boda, Upl</t>
+          <t>Kvistaren, Kvistaren, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696957</v>
+        <v>696887</v>
       </c>
       <c r="R8" t="n">
-        <v>6607497</v>
+        <v>6607691</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,12 +1377,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,22 +1407,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126693608</v>
+        <v>89925501</v>
       </c>
       <c r="B9" t="n">
-        <v>100625</v>
+        <v>4775</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,37 +1434,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Boda, Upl</t>
+          <t>Barrskog Öst Kvistaren, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697019</v>
+        <v>696915</v>
       </c>
       <c r="R9" t="n">
-        <v>6607522</v>
+        <v>6607618</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,12 +1497,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2021-01-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,28 +1516,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Fingal Gyllang</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
+          <t>Fingal Gyllang</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126693629</v>
+        <v>89925511</v>
       </c>
       <c r="B10" t="n">
-        <v>91838</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,37 +1546,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Boda, Upl</t>
+          <t>Barrskog Öst Kvistaren, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696922</v>
+        <v>696915</v>
       </c>
       <c r="R10" t="n">
-        <v>6607606</v>
+        <v>6607618</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,12 +1608,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,26 +1628,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Fingal Gyllang</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Stora Obrutna Skogsområden</t>
-        </is>
-      </c>
+          <t>Fingal Gyllang</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126693628</v>
+        <v>114930259</v>
       </c>
       <c r="B11" t="n">
-        <v>111309</v>
+        <v>8444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,34 +1651,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Boda, Upl</t>
+          <t>Björnmyra, Björnmyra, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697012</v>
+        <v>697027</v>
       </c>
       <c r="R11" t="n">
-        <v>6607512</v>
+        <v>6607714</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,12 +1711,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,19 +1741,718 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>89925545</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Barrskog Öst Kvistaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>696915</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6607618</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Roslags-Kulla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-01-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-01-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Fingal Gyllang</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fingal Gyllang</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126693628</v>
+      </c>
+      <c r="B13" t="n">
+        <v>111389</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Boda, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>697012</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6607512</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Roslags-Kulla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Aivars Dunskis</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Aivars Dunskis</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126693627</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Boda, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>697005</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6607495</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Roslags-Kulla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126693618</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Boda, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>696897</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6607722</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Roslags-Kulla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126693632</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Boda, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>696934</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6607745</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Roslags-Kulla</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126693608</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Boda, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>697019</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6607522</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Roslags-Kulla</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126693619</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Boda, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>696859</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6607593</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Roslags-Kulla</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31459-2025 artfynd.xlsx
+++ b/artfynd/A 31459-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126693623</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126693629</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89925465</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114931948</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126693620</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89925535</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114930157</t>
         </is>
       </c>
     </row>
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89925501</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89925511</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114930259</t>
         </is>
       </c>
     </row>
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89925545</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1960,6 +2020,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126693628</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2061,6 +2126,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126693627</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2158,6 +2228,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126693618</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2259,6 +2334,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126693632</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2356,6 +2436,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126693608</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2453,8 +2538,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126693619</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>